--- a/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.008279999999999999</v>
+        <v>0.0255</v>
       </c>
       <c r="E2">
-        <v>0.02862</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="F2">
-        <v>0.3675</v>
+        <v>0.0781</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>15180.8</v>
+        <v>17949.5</v>
       </c>
       <c r="L2">
-        <v>0.1957406096521597</v>
+        <v>0.1997458316501914</v>
       </c>
       <c r="M2">
-        <v>1587.345</v>
+        <v>8986.508</v>
       </c>
       <c r="N2">
-        <v>0.01389369562876972</v>
+        <v>0.07248785618757693</v>
       </c>
       <c r="O2">
-        <v>0.1045626712689713</v>
+        <v>0.5006550600295273</v>
       </c>
       <c r="P2">
-        <v>1587.345</v>
+        <v>8986.508</v>
       </c>
       <c r="Q2">
-        <v>0.01389369562876972</v>
+        <v>0.07248785618757693</v>
       </c>
       <c r="R2">
-        <v>0.1045626712689713</v>
+        <v>0.5006550600295273</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>654568.9</v>
+        <v>791622.9</v>
       </c>
       <c r="V2">
-        <v>5.729303374287633</v>
+        <v>6.38546662730313</v>
       </c>
       <c r="W2">
-        <v>0.07395272893898484</v>
+        <v>0.06722740089095777</v>
       </c>
       <c r="X2">
-        <v>0.2378800603182716</v>
+        <v>0.4317265546803146</v>
       </c>
       <c r="Y2">
-        <v>-0.1639273313792867</v>
+        <v>-0.3644991537893568</v>
       </c>
       <c r="Z2">
-        <v>0.1222007373417691</v>
+        <v>0.0989404238194619</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04168453990362237</v>
+        <v>0.06567966890812077</v>
       </c>
       <c r="AC2">
-        <v>-0.04168453990362237</v>
+        <v>-0.06567966890812077</v>
       </c>
       <c r="AD2">
-        <v>984040.3</v>
+        <v>1602345.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>984040.3</v>
+        <v>1602345.5</v>
       </c>
       <c r="AG2">
-        <v>329471.4</v>
+        <v>810722.6</v>
       </c>
       <c r="AH2">
-        <v>0.8959752509720569</v>
+        <v>0.9281866997745085</v>
       </c>
       <c r="AI2">
-        <v>0.8170970047895368</v>
+        <v>0.8579287244938362</v>
       </c>
       <c r="AJ2">
-        <v>0.7425197877854245</v>
+        <v>0.867365746609162</v>
       </c>
       <c r="AK2">
-        <v>0.5993180823503603</v>
+        <v>0.7534121920570432</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BNP Paribas SA (ENXTPA:BNP)</t>
+          <t>Crédit Agricole S.A. (ENXTPA:ACA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0137</v>
+        <v>0.0478</v>
       </c>
       <c r="E3">
-        <v>0.04849999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F3">
-        <v>0.13</v>
+        <v>0.0781</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>10169.2</v>
+        <v>5204.9</v>
       </c>
       <c r="L3">
-        <v>0.2031860967417735</v>
+        <v>0.2452284366799059</v>
       </c>
       <c r="M3">
-        <v>1587.345</v>
+        <v>3148.298</v>
       </c>
       <c r="N3">
-        <v>0.01866491934203703</v>
+        <v>0.09803414678196318</v>
       </c>
       <c r="O3">
-        <v>0.1560933996774574</v>
+        <v>0.6048719475878499</v>
       </c>
       <c r="P3">
-        <v>1587.345</v>
+        <v>3148.298</v>
       </c>
       <c r="Q3">
-        <v>0.01866491934203703</v>
+        <v>0.09803414678196318</v>
       </c>
       <c r="R3">
-        <v>0.1560933996774574</v>
+        <v>0.6048719475878499</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>449966.4</v>
+        <v>255148.1</v>
       </c>
       <c r="V3">
-        <v>5.29096482656686</v>
+        <v>7.944999579626522</v>
       </c>
       <c r="W3">
-        <v>0.07747023408211882</v>
+        <v>0.06722740089095777</v>
       </c>
       <c r="X3">
-        <v>0.1801197221794967</v>
+        <v>0.4844940980374246</v>
       </c>
       <c r="Y3">
-        <v>-0.1026494880973779</v>
+        <v>-0.4172666971464668</v>
       </c>
       <c r="Z3">
-        <v>0.1281139801196751</v>
+        <v>0.05535875064031873</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04132794095441643</v>
+        <v>0.06552716408298485</v>
       </c>
       <c r="AC3">
-        <v>-0.04132794095441643</v>
+        <v>-0.06552716408298485</v>
       </c>
       <c r="AD3">
-        <v>603749.4</v>
+        <v>593449.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>603749.4</v>
+        <v>593449.7</v>
       </c>
       <c r="AG3">
-        <v>153783</v>
+        <v>338301.6</v>
       </c>
       <c r="AH3">
-        <v>0.8765315362204967</v>
+        <v>0.9486634461062337</v>
       </c>
       <c r="AI3">
-        <v>0.8118012283724508</v>
+        <v>0.892230606208948</v>
       </c>
       <c r="AJ3">
-        <v>0.6439087993709263</v>
+        <v>0.9133020477792665</v>
       </c>
       <c r="AK3">
-        <v>0.5235176650573584</v>
+        <v>0.825161476483253</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,117 +829,245 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>BNP Paribas SA (ENXTPA:BNP)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0255</v>
+      </c>
+      <c r="E4">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.114</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>10151</v>
+      </c>
+      <c r="L4">
+        <v>0.2240641003001942</v>
+      </c>
+      <c r="M4">
+        <v>4483.08</v>
+      </c>
+      <c r="N4">
+        <v>0.06325967045728743</v>
+      </c>
+      <c r="O4">
+        <v>0.4416392473647917</v>
+      </c>
+      <c r="P4">
+        <v>4483.08</v>
+      </c>
+      <c r="Q4">
+        <v>0.06325967045728743</v>
+      </c>
+      <c r="R4">
+        <v>0.4416392473647917</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>339540.1</v>
+      </c>
+      <c r="V4">
+        <v>4.791169203546317</v>
+      </c>
+      <c r="W4">
+        <v>0.07539257838755989</v>
+      </c>
+      <c r="X4">
+        <v>0.2815484700518319</v>
+      </c>
+      <c r="Y4">
+        <v>-0.206155891664272</v>
+      </c>
+      <c r="Z4">
+        <v>0.1619038497550572</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06567966890812077</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06567966890812077</v>
+      </c>
+      <c r="AD4">
+        <v>670245.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>670245.1</v>
+      </c>
+      <c r="AG4">
+        <v>330705</v>
+      </c>
+      <c r="AH4">
+        <v>0.9043763906448814</v>
+      </c>
+      <c r="AI4">
+        <v>0.844950537412641</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8235241969764393</v>
+      </c>
+      <c r="AK4">
+        <v>0.7289135142974654</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Société Générale Société anonyme (ENXTPA:GLE)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.00286</v>
-      </c>
-      <c r="E4">
-        <v>0.00874</v>
-      </c>
-      <c r="F4">
-        <v>0.605</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>5011.6</v>
-      </c>
-      <c r="L4">
-        <v>0.1821936234413059</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>204602.5</v>
-      </c>
-      <c r="V4">
-        <v>7.005735319294641</v>
-      </c>
-      <c r="W4">
-        <v>0.07043522379585086</v>
-      </c>
-      <c r="X4">
-        <v>0.2956403984570464</v>
-      </c>
-      <c r="Y4">
-        <v>-0.2252051746611956</v>
-      </c>
-      <c r="Z4">
-        <v>0.1127333293442721</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.04204113885282831</v>
-      </c>
-      <c r="AC4">
-        <v>-0.04204113885282831</v>
-      </c>
-      <c r="AD4">
-        <v>380290.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>380290.9</v>
-      </c>
-      <c r="AG4">
-        <v>175688.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.9286806046165542</v>
-      </c>
-      <c r="AI4">
-        <v>0.8256479798279146</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8574624658480947</v>
-      </c>
-      <c r="AK4">
-        <v>0.6862978252649277</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.00049</v>
+      </c>
+      <c r="E5">
+        <v>-0.0329</v>
+      </c>
+      <c r="F5">
+        <v>-0.0493</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>2593.6</v>
+      </c>
+      <c r="L5">
+        <v>0.1111558736553379</v>
+      </c>
+      <c r="M5">
+        <v>1355.13</v>
+      </c>
+      <c r="N5">
+        <v>0.06455951292019209</v>
+      </c>
+      <c r="O5">
+        <v>0.5224899753238742</v>
+      </c>
+      <c r="P5">
+        <v>1355.13</v>
+      </c>
+      <c r="Q5">
+        <v>0.06455951292019209</v>
+      </c>
+      <c r="R5">
+        <v>0.5224899753238742</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>196934.7</v>
+      </c>
+      <c r="V5">
+        <v>9.382131831694489</v>
+      </c>
+      <c r="W5">
+        <v>0.03516388163915534</v>
+      </c>
+      <c r="X5">
+        <v>0.4317265546803146</v>
+      </c>
+      <c r="Y5">
+        <v>-0.3965626730411593</v>
+      </c>
+      <c r="Z5">
+        <v>0.09523001028906938</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06689319648868836</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06689319648868836</v>
+      </c>
+      <c r="AD5">
+        <v>338650.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>338650.7</v>
+      </c>
+      <c r="AG5">
+        <v>141716</v>
+      </c>
+      <c r="AH5">
+        <v>0.9416351468172018</v>
+      </c>
+      <c r="AI5">
+        <v>0.8273406129710322</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8709921674869582</v>
+      </c>
+      <c r="AK5">
+        <v>0.6672451630187339</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0255</v>
+        <v>0.0209</v>
       </c>
       <c r="E2">
-        <v>0.05889999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="F2">
-        <v>0.0781</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>17949.5</v>
+        <v>26838.4</v>
       </c>
       <c r="L2">
-        <v>0.1997458316501914</v>
+        <v>0.2414000599038839</v>
       </c>
       <c r="M2">
-        <v>8986.508</v>
+        <v>8128.214</v>
       </c>
       <c r="N2">
-        <v>0.07248785618757693</v>
+        <v>0.05649740596988367</v>
       </c>
       <c r="O2">
-        <v>0.5006550600295273</v>
+        <v>0.3028576219148682</v>
       </c>
       <c r="P2">
-        <v>8986.508</v>
+        <v>8128.214</v>
       </c>
       <c r="Q2">
-        <v>0.07248785618757693</v>
+        <v>0.05649740596988367</v>
       </c>
       <c r="R2">
-        <v>0.5006550600295273</v>
+        <v>0.3028576219148682</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>791622.9</v>
+        <v>699813.8</v>
       </c>
       <c r="V2">
-        <v>6.38546662730313</v>
+        <v>4.864249927711916</v>
       </c>
       <c r="W2">
-        <v>0.06722740089095777</v>
+        <v>0.1107944397577084</v>
       </c>
       <c r="X2">
-        <v>0.4317265546803146</v>
+        <v>0.2525505276496336</v>
       </c>
       <c r="Y2">
-        <v>-0.3644991537893568</v>
+        <v>-0.1417560878919252</v>
       </c>
       <c r="Z2">
-        <v>0.0989404238194619</v>
+        <v>0.1076358785810138</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06567966890812077</v>
+        <v>0.05619209795167444</v>
       </c>
       <c r="AC2">
-        <v>-0.06567966890812077</v>
+        <v>-0.05619209795167444</v>
       </c>
       <c r="AD2">
-        <v>1602345.5</v>
+        <v>1963707.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1602345.5</v>
+        <v>1963707.6</v>
       </c>
       <c r="AG2">
-        <v>810722.6</v>
+        <v>1263893.8</v>
       </c>
       <c r="AH2">
-        <v>0.9281866997745085</v>
+        <v>0.9317373263431874</v>
       </c>
       <c r="AI2">
-        <v>0.8579287244938362</v>
+        <v>0.8663685603270914</v>
       </c>
       <c r="AJ2">
-        <v>0.867365746609162</v>
+        <v>0.8978032233559834</v>
       </c>
       <c r="AK2">
-        <v>0.7534121920570432</v>
+        <v>0.8066811834675437</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0478</v>
+        <v>0.155</v>
       </c>
       <c r="E3">
-        <v>0.08359999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="F3">
-        <v>0.0781</v>
+        <v>0.0861</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>5204.9</v>
+        <v>10197.9</v>
       </c>
       <c r="L3">
-        <v>0.2452284366799059</v>
+        <v>0.25569156244672</v>
       </c>
       <c r="M3">
-        <v>3148.298</v>
+        <v>3387.387</v>
       </c>
       <c r="N3">
-        <v>0.09803414678196318</v>
+        <v>0.07813807198400048</v>
       </c>
       <c r="O3">
-        <v>0.6048719475878499</v>
+        <v>0.3321651516488689</v>
       </c>
       <c r="P3">
-        <v>3148.298</v>
+        <v>3387.387</v>
       </c>
       <c r="Q3">
-        <v>0.09803414678196318</v>
+        <v>0.07813807198400048</v>
       </c>
       <c r="R3">
-        <v>0.6048719475878499</v>
+        <v>0.3321651516488689</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>255148.1</v>
+        <v>166490.3</v>
       </c>
       <c r="V3">
-        <v>7.944999579626522</v>
+        <v>3.840491519285465</v>
       </c>
       <c r="W3">
-        <v>0.06722740089095777</v>
+        <v>0.1617389566640656</v>
       </c>
       <c r="X3">
-        <v>0.4844940980374246</v>
+        <v>0.2525505276496336</v>
       </c>
       <c r="Y3">
-        <v>-0.4172666971464668</v>
+        <v>-0.09081157098556802</v>
       </c>
       <c r="Z3">
-        <v>0.05535875064031873</v>
+        <v>0.1033366324833272</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06552716408298485</v>
+        <v>0.0560664560074353</v>
       </c>
       <c r="AC3">
-        <v>-0.06552716408298485</v>
+        <v>-0.0560664560074353</v>
       </c>
       <c r="AD3">
-        <v>593449.7</v>
+        <v>531964.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>593449.7</v>
+        <v>531964.4</v>
       </c>
       <c r="AG3">
-        <v>338301.6</v>
+        <v>365474.1</v>
       </c>
       <c r="AH3">
-        <v>0.9486634461062337</v>
+        <v>0.9246478064130702</v>
       </c>
       <c r="AI3">
-        <v>0.892230606208948</v>
+        <v>0.8647625661498227</v>
       </c>
       <c r="AJ3">
-        <v>0.9133020477792665</v>
+        <v>0.8939613341049749</v>
       </c>
       <c r="AK3">
-        <v>0.825161476483253</v>
+        <v>0.8145788975013278</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0255</v>
+        <v>0.0209</v>
       </c>
       <c r="E4">
-        <v>0.05889999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="F4">
-        <v>0.114</v>
+        <v>0.128</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>10151</v>
+        <v>13120.2</v>
       </c>
       <c r="L4">
-        <v>0.2240641003001942</v>
+        <v>0.2746661977315262</v>
       </c>
       <c r="M4">
-        <v>4483.08</v>
+        <v>4740.827</v>
       </c>
       <c r="N4">
-        <v>0.06325967045728743</v>
+        <v>0.05969687086822389</v>
       </c>
       <c r="O4">
-        <v>0.4416392473647917</v>
+        <v>0.3613380131400436</v>
       </c>
       <c r="P4">
-        <v>4483.08</v>
+        <v>4740.827</v>
       </c>
       <c r="Q4">
-        <v>0.06325967045728743</v>
+        <v>0.05969687086822389</v>
       </c>
       <c r="R4">
-        <v>0.4416392473647917</v>
+        <v>0.3613380131400436</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>339540.1</v>
+        <v>285647.8</v>
       </c>
       <c r="V4">
-        <v>4.791169203546317</v>
+        <v>3.596899830006925</v>
       </c>
       <c r="W4">
-        <v>0.07539257838755989</v>
+        <v>0.1107944397577084</v>
       </c>
       <c r="X4">
-        <v>0.2815484700518319</v>
+        <v>0.1910185365378683</v>
       </c>
       <c r="Y4">
-        <v>-0.206155891664272</v>
+        <v>-0.08022409678015988</v>
       </c>
       <c r="Z4">
-        <v>0.1619038497550572</v>
+        <v>0.1076015904234003</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06567966890812077</v>
+        <v>0.05619209795167444</v>
       </c>
       <c r="AC4">
-        <v>-0.06567966890812077</v>
+        <v>-0.05619209795167444</v>
       </c>
       <c r="AD4">
-        <v>670245.1</v>
+        <v>663492.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>670245.1</v>
+        <v>663492.8</v>
       </c>
       <c r="AG4">
-        <v>330705</v>
+        <v>377845.0000000001</v>
       </c>
       <c r="AH4">
-        <v>0.9043763906448814</v>
+        <v>0.8931024818961384</v>
       </c>
       <c r="AI4">
-        <v>0.844950537412641</v>
+        <v>0.8289930567485952</v>
       </c>
       <c r="AJ4">
-        <v>0.8235241969764393</v>
+        <v>0.8263241919258191</v>
       </c>
       <c r="AK4">
-        <v>0.7289135142974654</v>
+        <v>0.734089989335786</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00049</v>
+        <v>-0.0291</v>
       </c>
       <c r="E5">
-        <v>-0.0329</v>
+        <v>-0.0104</v>
       </c>
       <c r="F5">
-        <v>-0.0493</v>
+        <v>0.175</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2593.6</v>
+        <v>3520.3</v>
       </c>
       <c r="L5">
-        <v>0.1111558736553379</v>
+        <v>0.1496299948569073</v>
       </c>
       <c r="M5">
-        <v>1355.13</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.06455951292019209</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.5224899753238742</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>1355.13</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.06455951292019209</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.5224899753238742</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>196934.7</v>
+        <v>247675.7</v>
       </c>
       <c r="V5">
-        <v>9.382131831694489</v>
+        <v>11.73679421869447</v>
       </c>
       <c r="W5">
-        <v>0.03516388163915534</v>
+        <v>0.05413888824809492</v>
       </c>
       <c r="X5">
-        <v>0.4317265546803146</v>
+        <v>0.6317523305833568</v>
       </c>
       <c r="Y5">
-        <v>-0.3965626730411593</v>
+        <v>-0.5776134423352619</v>
       </c>
       <c r="Z5">
-        <v>0.09523001028906938</v>
+        <v>0.115884113423755</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06689319648868836</v>
+        <v>0.05696189892918646</v>
       </c>
       <c r="AC5">
-        <v>-0.06689319648868836</v>
+        <v>-0.05696189892918646</v>
       </c>
       <c r="AD5">
-        <v>338650.7</v>
+        <v>768250.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>338650.7</v>
+        <v>768250.4</v>
       </c>
       <c r="AG5">
-        <v>141716</v>
+        <v>520574.7</v>
       </c>
       <c r="AH5">
-        <v>0.9416351468172018</v>
+        <v>0.9732660765546057</v>
       </c>
       <c r="AI5">
-        <v>0.8273406129710322</v>
+        <v>0.9026774933860476</v>
       </c>
       <c r="AJ5">
-        <v>0.8709921674869582</v>
+        <v>0.9610422960390432</v>
       </c>
       <c r="AK5">
-        <v>0.6672451630187339</v>
+        <v>0.8627300884200449</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0209</v>
+        <v>0.0143</v>
       </c>
       <c r="E2">
-        <v>0.105</v>
+        <v>0.0609</v>
       </c>
       <c r="F2">
-        <v>0.128</v>
+        <v>0.155</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>26838.4</v>
+        <v>25281</v>
       </c>
       <c r="L2">
-        <v>0.2414000599038839</v>
+        <v>0.2184660453420094</v>
       </c>
       <c r="M2">
-        <v>8128.214</v>
+        <v>10144.774</v>
       </c>
       <c r="N2">
-        <v>0.05649740596988367</v>
+        <v>0.07598227914466539</v>
       </c>
       <c r="O2">
-        <v>0.3028576219148682</v>
+        <v>0.4012805664332898</v>
       </c>
       <c r="P2">
-        <v>8128.214</v>
+        <v>10144.774</v>
       </c>
       <c r="Q2">
-        <v>0.05649740596988367</v>
+        <v>0.07598227914466539</v>
       </c>
       <c r="R2">
-        <v>0.3028576219148682</v>
+        <v>0.4012805664332898</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>699813.8</v>
+        <v>615428.3</v>
       </c>
       <c r="V2">
-        <v>4.864249927711916</v>
+        <v>4.609431899037562</v>
       </c>
       <c r="W2">
-        <v>0.1107944397577084</v>
+        <v>0.08857850016896161</v>
       </c>
       <c r="X2">
-        <v>0.2525505276496336</v>
+        <v>0.2674542649329398</v>
       </c>
       <c r="Y2">
-        <v>-0.1417560878919252</v>
+        <v>-0.1788757647639782</v>
       </c>
       <c r="Z2">
-        <v>0.1076358785810138</v>
+        <v>0.07651012968053918</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05619209795167444</v>
+        <v>0.06029266348925039</v>
       </c>
       <c r="AC2">
-        <v>-0.05619209795167444</v>
+        <v>-0.06029266348925039</v>
       </c>
       <c r="AD2">
-        <v>1963707.6</v>
+        <v>1598199.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1963707.6</v>
+        <v>1598199.8</v>
       </c>
       <c r="AG2">
-        <v>1263893.8</v>
+        <v>982771.5</v>
       </c>
       <c r="AH2">
-        <v>0.9317373263431874</v>
+        <v>0.9229001218907409</v>
       </c>
       <c r="AI2">
-        <v>0.8663685603270914</v>
+        <v>0.8329071428284794</v>
       </c>
       <c r="AJ2">
-        <v>0.8978032233559834</v>
+        <v>0.8803936086300426</v>
       </c>
       <c r="AK2">
-        <v>0.8066811834675437</v>
+        <v>0.7540102262341789</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.155</v>
+        <v>0.13</v>
       </c>
       <c r="E3">
-        <v>0.206</v>
+        <v>0.156</v>
       </c>
       <c r="F3">
-        <v>0.0861</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>10197.9</v>
+        <v>9637.5</v>
       </c>
       <c r="L3">
-        <v>0.25569156244672</v>
+        <v>0.2504196396555577</v>
       </c>
       <c r="M3">
-        <v>3387.387</v>
+        <v>3557.034</v>
       </c>
       <c r="N3">
-        <v>0.07813807198400048</v>
+        <v>0.08503405393646293</v>
       </c>
       <c r="O3">
-        <v>0.3321651516488689</v>
+        <v>0.3690826459143969</v>
       </c>
       <c r="P3">
-        <v>3387.387</v>
+        <v>3557.034</v>
       </c>
       <c r="Q3">
-        <v>0.07813807198400048</v>
+        <v>0.08503405393646293</v>
       </c>
       <c r="R3">
-        <v>0.3321651516488689</v>
+        <v>0.3690826459143969</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>166490.3</v>
+        <v>184809.3</v>
       </c>
       <c r="V3">
-        <v>3.840491519285465</v>
+        <v>4.418030298321567</v>
       </c>
       <c r="W3">
-        <v>0.1617389566640656</v>
+        <v>0.1312033130623364</v>
       </c>
       <c r="X3">
-        <v>0.2525505276496336</v>
+        <v>0.2674542649329398</v>
       </c>
       <c r="Y3">
-        <v>-0.09081157098556802</v>
+        <v>-0.1362509518706035</v>
       </c>
       <c r="Z3">
-        <v>0.1033366324833272</v>
+        <v>0.09117606783988053</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0560664560074353</v>
+        <v>0.06016970451736817</v>
       </c>
       <c r="AC3">
-        <v>-0.0560664560074353</v>
+        <v>-0.06016970451736817</v>
       </c>
       <c r="AD3">
-        <v>531964.4</v>
+        <v>556100.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>531964.4</v>
+        <v>556100.8</v>
       </c>
       <c r="AG3">
-        <v>365474.1</v>
+        <v>371291.5000000001</v>
       </c>
       <c r="AH3">
-        <v>0.9246478064130702</v>
+        <v>0.9300409829554055</v>
       </c>
       <c r="AI3">
-        <v>0.8647625661498227</v>
+        <v>0.8624805376064082</v>
       </c>
       <c r="AJ3">
-        <v>0.8939613341049749</v>
+        <v>0.898744971826738</v>
       </c>
       <c r="AK3">
-        <v>0.8145788975013278</v>
+        <v>0.8072259793138444</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0209</v>
+        <v>0.0143</v>
       </c>
       <c r="E4">
-        <v>0.105</v>
+        <v>0.0609</v>
       </c>
       <c r="F4">
-        <v>0.128</v>
+        <v>0.155</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>13120.2</v>
+        <v>11638.4</v>
       </c>
       <c r="L4">
-        <v>0.2746661977315262</v>
+        <v>0.2335597676122054</v>
       </c>
       <c r="M4">
-        <v>4740.827</v>
+        <v>5786.64</v>
       </c>
       <c r="N4">
-        <v>0.05969687086822389</v>
+        <v>0.0836721444218715</v>
       </c>
       <c r="O4">
-        <v>0.3613380131400436</v>
+        <v>0.4972023645861974</v>
       </c>
       <c r="P4">
-        <v>4740.827</v>
+        <v>5786.64</v>
       </c>
       <c r="Q4">
-        <v>0.05969687086822389</v>
+        <v>0.0836721444218715</v>
       </c>
       <c r="R4">
-        <v>0.3613380131400436</v>
+        <v>0.4972023645861974</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>285647.8</v>
+        <v>208513.3</v>
       </c>
       <c r="V4">
-        <v>3.596899830006925</v>
+        <v>3.015006109155057</v>
       </c>
       <c r="W4">
-        <v>0.1107944397577084</v>
+        <v>0.08857850016896161</v>
       </c>
       <c r="X4">
-        <v>0.1910185365378683</v>
+        <v>0.2200520308705667</v>
       </c>
       <c r="Y4">
-        <v>-0.08022409678015988</v>
+        <v>-0.1314735307016051</v>
       </c>
       <c r="Z4">
-        <v>0.1076015904234003</v>
+        <v>0.0990054453441979</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05619209795167444</v>
+        <v>0.06029266348925039</v>
       </c>
       <c r="AC4">
-        <v>-0.05619209795167444</v>
+        <v>-0.06029266348925039</v>
       </c>
       <c r="AD4">
-        <v>663492.8</v>
+        <v>703059.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>663492.8</v>
+        <v>703059.3</v>
       </c>
       <c r="AG4">
-        <v>377845.0000000001</v>
+        <v>494546.0000000001</v>
       </c>
       <c r="AH4">
-        <v>0.8931024818961384</v>
+        <v>0.9104417173496907</v>
       </c>
       <c r="AI4">
-        <v>0.8289930567485952</v>
+        <v>0.828234915203202</v>
       </c>
       <c r="AJ4">
-        <v>0.8263241919258191</v>
+        <v>0.8773142666059967</v>
       </c>
       <c r="AK4">
-        <v>0.734089989335786</v>
+        <v>0.7723042023964034</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0291</v>
+        <v>0.0121</v>
       </c>
       <c r="E5">
-        <v>-0.0104</v>
+        <v>0.0183</v>
       </c>
       <c r="F5">
-        <v>0.175</v>
+        <v>0.291</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,82 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3520.3</v>
+        <v>4005.1</v>
       </c>
       <c r="L5">
-        <v>0.1496299948569073</v>
+        <v>0.1461469972194449</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>801.1</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03556366477550187</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.2000199745324711</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>801.1</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03556366477550187</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.2000199745324711</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>247675.7</v>
+        <v>222105.7</v>
       </c>
       <c r="V5">
-        <v>11.73679421869447</v>
+        <v>9.860058244324287</v>
       </c>
       <c r="W5">
-        <v>0.05413888824809492</v>
+        <v>0.05558439179286762</v>
       </c>
       <c r="X5">
-        <v>0.6317523305833568</v>
+        <v>0.2940800438495889</v>
       </c>
       <c r="Y5">
-        <v>-0.5776134423352619</v>
+        <v>-0.2384956520567212</v>
       </c>
       <c r="Z5">
-        <v>0.115884113423755</v>
+        <v>0.04667985633875028</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05696189892918646</v>
+        <v>0.06068427873637689</v>
       </c>
       <c r="AC5">
-        <v>-0.05696189892918646</v>
+        <v>-0.06068427873637689</v>
       </c>
       <c r="AD5">
-        <v>768250.4</v>
+        <v>339039.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>768250.4</v>
+        <v>339039.7</v>
       </c>
       <c r="AG5">
-        <v>520574.7</v>
+        <v>116934</v>
       </c>
       <c r="AH5">
-        <v>0.9732660765546057</v>
+        <v>0.9376992550450749</v>
       </c>
       <c r="AI5">
-        <v>0.9026774933860476</v>
+        <v>0.7973888690022329</v>
       </c>
       <c r="AJ5">
-        <v>0.9610422960390432</v>
+        <v>0.8384781851114085</v>
       </c>
       <c r="AK5">
-        <v>0.8627300884200449</v>
+        <v>0.5757978193012959</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/france/france_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.08857850016896161</v>
       </c>
       <c r="X2">
-        <v>0.2674542649329398</v>
+        <v>0.2673507502059392</v>
       </c>
       <c r="Y2">
-        <v>-0.1788757647639782</v>
+        <v>-0.1787722500369776</v>
       </c>
       <c r="Z2">
         <v>0.07651012968053918</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06029266348925039</v>
+        <v>0.06028537546759489</v>
       </c>
       <c r="AC2">
-        <v>-0.06029266348925039</v>
+        <v>-0.06028537546759489</v>
       </c>
       <c r="AD2">
         <v>1598199.8</v>
@@ -773,10 +773,10 @@
         <v>0.1312033130623364</v>
       </c>
       <c r="X3">
-        <v>0.2674542649329398</v>
+        <v>0.2673507502059392</v>
       </c>
       <c r="Y3">
-        <v>-0.1362509518706035</v>
+        <v>-0.1361474371436028</v>
       </c>
       <c r="Z3">
         <v>0.09117606783988053</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06016970451736817</v>
+        <v>0.06016246272881756</v>
       </c>
       <c r="AC3">
-        <v>-0.06016970451736817</v>
+        <v>-0.06016246272881756</v>
       </c>
       <c r="AD3">
         <v>556100.8</v>
@@ -898,10 +898,10 @@
         <v>0.08857850016896161</v>
       </c>
       <c r="X4">
-        <v>0.2200520308705667</v>
+        <v>0.2199706534542092</v>
       </c>
       <c r="Y4">
-        <v>-0.1314735307016051</v>
+        <v>-0.1313921532852476</v>
       </c>
       <c r="Z4">
         <v>0.0990054453441979</v>
@@ -910,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06029266348925039</v>
+        <v>0.06028537546759489</v>
       </c>
       <c r="AC4">
-        <v>-0.06029266348925039</v>
+        <v>-0.06028537546759489</v>
       </c>
       <c r="AD4">
         <v>703059.3</v>
@@ -1023,10 +1023,10 @@
         <v>0.05558439179286762</v>
       </c>
       <c r="X5">
-        <v>0.2940800438495889</v>
+        <v>0.2939640946213321</v>
       </c>
       <c r="Y5">
-        <v>-0.2384956520567212</v>
+        <v>-0.2383797028284645</v>
       </c>
       <c r="Z5">
         <v>0.04667985633875028</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06068427873637689</v>
+        <v>0.06067705501307954</v>
       </c>
       <c r="AC5">
-        <v>-0.06068427873637689</v>
+        <v>-0.06067705501307954</v>
       </c>
       <c r="AD5">
         <v>339039.7</v>
